--- a/etf_holdings/2026-10-29_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:09</t>
+          <t>2026-10-29 23:21:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.04%2425</t>
+          <t>-0.41%2415</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:10</t>
+          <t>2026-10-29 23:21:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,27 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.77%1100</t>
+          <t>-5.45%1040</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.09%667,000</t>
+          <t>2.15%667,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:10</t>
+          <t>2026-10-29 23:21:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,40 +630,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6098RECRUIT HOLDINGS CO LTD</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.49%4045</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.99%174,100</t>
+          <t>2.05%165,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>174100</v>
+        <v>165000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:10</t>
+          <t>2026-10-29 23:21:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -693,40 +693,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+6.94%4235</t>
+          <t>-0.3%5010</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+6.94%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.93%165,000</t>
+          <t>1.97%134,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>165000</v>
+        <v>134000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:10</t>
+          <t>2026-10-29 23:21:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,40 +756,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6098RECRUIT HOLDINGS CO LTD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.65%1550</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.88%420,000</t>
+          <t>1.97%174,100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>420000</v>
+        <v>174100</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:10</t>
+          <t>2026-10-29 23:21:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -819,40 +819,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.79%5025</t>
+          <t>-4.52%1480</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>-4.52%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.88%134,000</t>
+          <t>1.91%420,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>134000</v>
+        <v>420000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:10</t>
+          <t>2026-10-29 23:21:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,27 +887,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.72%3215</t>
+          <t>-3.42%3105</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.72%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.46%158,000</t>
+          <t>1.49%158,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:11</t>
+          <t>2026-10-29 23:21:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,27 +950,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.59%1300</t>
+          <t>-3.85%1250</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.59%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.29%348,000</t>
+          <t>1.33%348,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:11</t>
+          <t>2026-10-29 23:21:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,35 +1013,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+9.72%1185</t>
+          <t>-5.91%1115</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+9.72%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.11%346,000</t>
+          <t>1.28%368,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>346000</v>
+        <v>368000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:11</t>
+          <t>2026-10-29 23:21:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,40 +1071,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.13%1815</t>
+          <t>-6.49%7640</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-6.49%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.01%193,000</t>
+          <t>1.05%44,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>193000</v>
+        <v>44000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:11</t>
+          <t>2026-10-29 23:21:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,40 +1134,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+9.96%8170</t>
+          <t>-3.31%1755</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.97%44,000</t>
+          <t>1.03%193,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>44000</v>
+        <v>193000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">

--- a/etf_holdings/2026-10-29_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:26</t>
+          <t>2026-10-29 23:34:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:29</t>
+          <t>2026-10-29 23:34:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:29</t>
+          <t>2026-10-29 23:34:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:29</t>
+          <t>2026-10-29 23:34:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:29</t>
+          <t>2026-10-29 23:34:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
